--- a/outputs/Results/PSM_res.xlsx
+++ b/outputs/Results/PSM_res.xlsx
@@ -425,40 +425,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV3"/>
+  <dimension ref="A1:AN3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>target_optimization</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ablation</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>data</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>entity_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>ablation</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>downsample</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>mixerType</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>downsample</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>target_optimization</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>seed</t>
@@ -586,113 +586,73 @@
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>avgVUS_ROC</t>
+          <t>avggflops</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>avgVUS_PR</t>
+          <t>avgavgInfTime</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>avggflops</t>
+          <t>avgnParams</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>avgavgInfTime</t>
+          <t>alphas</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>avgnParams</t>
+          <t>f1_concat</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>alphas</t>
+          <t>TP_concat</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>f1_concat</t>
+          <t>FP_concat</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>TP_concat</t>
+          <t>TN_concat</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>FP_concat</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>TN_concat</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
           <t>FN_concat</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>avgAff_F1</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>avgAff_P</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>avgAff_R</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>avgRange_F1</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>avgRange_P</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>avgRange_R</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>pf1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>PSM</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>causal</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>pf1</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -768,73 +728,61 @@
         <v>0.6565702781844802</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.5358263296343584</v>
+        <v>0.5358258437706805</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>3.545137152</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>0.00102213648862617</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.545137152</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0.001913166323373484</v>
+        <v>144197</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[0]</t>
+        </is>
       </c>
       <c r="AJ2" t="n">
-        <v>144197</v>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>[0]</t>
-        </is>
+        <v>0.6565702781844802</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>21525</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.6565702781844802</v>
+        <v>19662</v>
       </c>
       <c r="AM2" t="n">
-        <v>21525</v>
+        <v>43775</v>
       </c>
       <c r="AN2" t="n">
-        <v>19662</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>43775</v>
-      </c>
-      <c r="AP2" t="n">
         <v>2856</v>
       </c>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>sf1</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>PSM</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>causal</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>sf1</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -886,84 +834,60 @@
         <v>4</v>
       </c>
       <c r="W3" t="n">
-        <v>20620</v>
+        <v>20625</v>
       </c>
       <c r="X3" t="n">
-        <v>12616</v>
+        <v>12619</v>
       </c>
       <c r="Y3" t="n">
-        <v>50821</v>
+        <v>50818</v>
       </c>
       <c r="Z3" t="n">
-        <v>3761</v>
+        <v>3756</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8457405356630163</v>
+        <v>0.8459456133874739</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.6204116018774822</v>
+        <v>0.62041270605222</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1988744738874789</v>
+        <v>0.1989217649006101</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.7157609733238454</v>
+        <v>0.7158351409978309</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.55833764577815</v>
+        <v>0.5583746856683476</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.5445585711951022</v>
+        <v>3.545137152</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.4851841972118994</v>
+        <v>0.001203482927278031</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.545137152</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0.001821328041165374</v>
+        <v>144197</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[0.5563026489809617]</t>
+        </is>
       </c>
       <c r="AJ3" t="n">
-        <v>144197</v>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>[0.5561137773003815]</t>
-        </is>
+        <v>0.7158351409978309</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>20625</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.7157609733238454</v>
+        <v>12619</v>
       </c>
       <c r="AM3" t="n">
-        <v>20620</v>
+        <v>50818</v>
       </c>
       <c r="AN3" t="n">
-        <v>12616</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>50821</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>3761</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0.6942863752915319</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0.5317294406317833</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0.4281198079995865</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0.4610341960046392</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0.3995919370241116</v>
+        <v>3756</v>
       </c>
     </row>
   </sheetData>
